--- a/Data/permobil_data.xlsx
+++ b/Data/permobil_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ10"/>
+  <dimension ref="A1:BJ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2270,6 +2270,176 @@
         <v>2.375</v>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E11" t="n">
+        <v>13</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>19</v>
+      </c>
+      <c r="H11" t="n">
+        <v>7</v>
+      </c>
+      <c r="I11" t="n">
+        <v>7</v>
+      </c>
+      <c r="J11" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" t="n">
+        <v>25</v>
+      </c>
+      <c r="L11" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" t="n">
+        <v>20</v>
+      </c>
+      <c r="N11" t="n">
+        <v>3</v>
+      </c>
+      <c r="O11" t="n">
+        <v>9</v>
+      </c>
+      <c r="P11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>24</v>
+      </c>
+      <c r="R11" t="n">
+        <v>5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>6</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>75</v>
+      </c>
+      <c r="V11" t="n">
+        <v>3</v>
+      </c>
+      <c r="W11" t="n">
+        <v>18</v>
+      </c>
+      <c r="X11" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>102</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC11" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF11" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG11" t="n">
+        <v>1.115</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>1.333</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.5</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/permobil_data.xlsx
+++ b/Data/permobil_data.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ11"/>
+  <dimension ref="A1:BJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2273,113 +2273,113 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>P12</t>
+          <t>P10</t>
         </is>
       </c>
       <c r="B11" t="n">
         <v>3</v>
       </c>
       <c r="C11" t="n">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="D11" t="n">
         <v>3</v>
       </c>
       <c r="E11" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
         <v>3</v>
       </c>
       <c r="G11" t="n">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="H11" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="I11" t="n">
         <v>7</v>
       </c>
       <c r="J11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K11" t="n">
+        <v>38</v>
+      </c>
+      <c r="L11" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" t="n">
+        <v>37</v>
+      </c>
+      <c r="N11" t="n">
+        <v>2</v>
+      </c>
+      <c r="O11" t="n">
         <v>25</v>
       </c>
-      <c r="L11" t="n">
-        <v>3</v>
-      </c>
-      <c r="M11" t="n">
-        <v>20</v>
-      </c>
-      <c r="N11" t="n">
-        <v>3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>9</v>
-      </c>
       <c r="P11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q11" t="n">
-        <v>24</v>
+        <v>190</v>
       </c>
       <c r="R11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="T11" t="n">
         <v>3</v>
       </c>
       <c r="U11" t="n">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="V11" t="n">
         <v>3</v>
       </c>
       <c r="W11" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="X11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y11" t="n">
-        <v>75</v>
+        <v>168</v>
       </c>
       <c r="Z11" t="n">
         <v>2</v>
       </c>
       <c r="AA11" t="n">
+        <v>143</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>2</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>332</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE11" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF11" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG11" t="n">
         <v>34</v>
       </c>
-      <c r="AB11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>102</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>4</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>6</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>3</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12</v>
-      </c>
       <c r="AH11" t="n">
         <v>3</v>
       </c>
       <c r="AI11" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="inlineStr"/>
       <c r="AL11" t="n">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="AM11" t="inlineStr"/>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AO11" t="n">
         <v>7</v>
@@ -2416,27 +2416,339 @@
         <v>6</v>
       </c>
       <c r="BC11" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD11" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE11" t="n">
         <v>4</v>
       </c>
-      <c r="BD11" t="n">
-        <v>5</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>6</v>
-      </c>
       <c r="BF11" t="n">
         <v>0</v>
       </c>
       <c r="BG11" t="n">
+        <v>0.269</v>
+      </c>
+      <c r="BH11" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="BI11" t="n">
+        <v>0.667</v>
+      </c>
+      <c r="BJ11" t="n">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>P11</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3</v>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="n">
+        <v>3</v>
+      </c>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="n">
+        <v>3</v>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="n">
+        <v>7</v>
+      </c>
+      <c r="I12" t="n">
+        <v>7</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3</v>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="n">
+        <v>3</v>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="n">
+        <v>3</v>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="n">
+        <v>5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>6</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="n">
+        <v>3</v>
+      </c>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE12" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC12" t="n">
+        <v>6</v>
+      </c>
+      <c r="BD12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE12" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF12" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG12" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BH12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BI12" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="BJ12" t="n">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>P12</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>3</v>
+      </c>
+      <c r="C13" t="n">
+        <v>15</v>
+      </c>
+      <c r="D13" t="n">
+        <v>3</v>
+      </c>
+      <c r="E13" t="n">
+        <v>13</v>
+      </c>
+      <c r="F13" t="n">
+        <v>3</v>
+      </c>
+      <c r="G13" t="n">
+        <v>19</v>
+      </c>
+      <c r="H13" t="n">
+        <v>7</v>
+      </c>
+      <c r="I13" t="n">
+        <v>7</v>
+      </c>
+      <c r="J13" t="n">
+        <v>3</v>
+      </c>
+      <c r="K13" t="n">
+        <v>25</v>
+      </c>
+      <c r="L13" t="n">
+        <v>3</v>
+      </c>
+      <c r="M13" t="n">
+        <v>20</v>
+      </c>
+      <c r="N13" t="n">
+        <v>3</v>
+      </c>
+      <c r="O13" t="n">
+        <v>9</v>
+      </c>
+      <c r="P13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>24</v>
+      </c>
+      <c r="R13" t="n">
+        <v>5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>6</v>
+      </c>
+      <c r="T13" t="n">
+        <v>3</v>
+      </c>
+      <c r="U13" t="n">
+        <v>75</v>
+      </c>
+      <c r="V13" t="n">
+        <v>3</v>
+      </c>
+      <c r="W13" t="n">
+        <v>18</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>34</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>102</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI13" t="n">
+        <v>12</v>
+      </c>
+      <c r="AJ13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG13" t="n">
         <v>1.115</v>
       </c>
-      <c r="BH11" t="n">
+      <c r="BH13" t="n">
         <v>1.417</v>
       </c>
-      <c r="BI11" t="n">
+      <c r="BI13" t="n">
         <v>1.333</v>
       </c>
-      <c r="BJ11" t="n">
+      <c r="BJ13" t="n">
         <v>0.5</v>
       </c>
     </row>

--- a/Data/permobil_data.xlsx
+++ b/Data/permobil_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ13"/>
+  <dimension ref="A1:BJ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2449,15 +2449,21 @@
       <c r="B12" t="n">
         <v>3</v>
       </c>
-      <c r="C12" t="inlineStr"/>
+      <c r="C12" t="n">
+        <v>45</v>
+      </c>
       <c r="D12" t="n">
         <v>3</v>
       </c>
-      <c r="E12" t="inlineStr"/>
+      <c r="E12" t="n">
+        <v>16</v>
+      </c>
       <c r="F12" t="n">
         <v>3</v>
       </c>
-      <c r="G12" t="inlineStr"/>
+      <c r="G12" t="n">
+        <v>26</v>
+      </c>
       <c r="H12" t="n">
         <v>7</v>
       </c>
@@ -2467,19 +2473,27 @@
       <c r="J12" t="n">
         <v>3</v>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="n">
+        <v>28</v>
+      </c>
       <c r="L12" t="n">
         <v>3</v>
       </c>
-      <c r="M12" t="inlineStr"/>
+      <c r="M12" t="n">
+        <v>26</v>
+      </c>
       <c r="N12" t="n">
         <v>3</v>
       </c>
-      <c r="O12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>7</v>
+      </c>
       <c r="P12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="inlineStr"/>
+      <c r="Q12" t="n">
+        <v>51</v>
+      </c>
       <c r="R12" t="n">
         <v>5</v>
       </c>
@@ -2489,23 +2503,33 @@
       <c r="T12" t="n">
         <v>3</v>
       </c>
-      <c r="U12" t="inlineStr"/>
+      <c r="U12" t="n">
+        <v>54</v>
+      </c>
       <c r="V12" t="n">
         <v>3</v>
       </c>
-      <c r="W12" t="inlineStr"/>
+      <c r="W12" t="n">
+        <v>23</v>
+      </c>
       <c r="X12" t="n">
         <v>3</v>
       </c>
-      <c r="Y12" t="inlineStr"/>
+      <c r="Y12" t="n">
+        <v>149</v>
+      </c>
       <c r="Z12" t="n">
         <v>1</v>
       </c>
-      <c r="AA12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>137</v>
+      </c>
       <c r="AB12" t="n">
-        <v>3</v>
-      </c>
-      <c r="AC12" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="AC12" t="n">
+        <v>60</v>
+      </c>
       <c r="AD12" t="n">
         <v>4</v>
       </c>
@@ -2515,11 +2539,15 @@
       <c r="AF12" t="n">
         <v>3</v>
       </c>
-      <c r="AG12" t="inlineStr"/>
+      <c r="AG12" t="n">
+        <v>8</v>
+      </c>
       <c r="AH12" t="n">
         <v>3</v>
       </c>
-      <c r="AI12" t="inlineStr"/>
+      <c r="AI12" t="n">
+        <v>9</v>
+      </c>
       <c r="AJ12" t="n">
         <v>0</v>
       </c>
@@ -2570,13 +2598,13 @@
         <v>0</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.73</v>
+        <v>1.731</v>
       </c>
       <c r="BH12" t="n">
-        <v>1.83</v>
+        <v>1.833</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.83</v>
+        <v>1.833</v>
       </c>
       <c r="BJ12" t="n">
         <v>1.5</v>
@@ -2750,6 +2778,514 @@
       </c>
       <c r="BJ13" t="n">
         <v>0.5</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>P13</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>3</v>
+      </c>
+      <c r="C14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D14" t="n">
+        <v>3</v>
+      </c>
+      <c r="E14" t="n">
+        <v>15</v>
+      </c>
+      <c r="F14" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" t="n">
+        <v>14</v>
+      </c>
+      <c r="H14" t="n">
+        <v>7</v>
+      </c>
+      <c r="I14" t="n">
+        <v>7</v>
+      </c>
+      <c r="J14" t="n">
+        <v>3</v>
+      </c>
+      <c r="K14" t="n">
+        <v>44</v>
+      </c>
+      <c r="L14" t="n">
+        <v>3</v>
+      </c>
+      <c r="M14" t="n">
+        <v>27</v>
+      </c>
+      <c r="N14" t="n">
+        <v>3</v>
+      </c>
+      <c r="O14" t="n">
+        <v>10</v>
+      </c>
+      <c r="P14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>74</v>
+      </c>
+      <c r="R14" t="n">
+        <v>5</v>
+      </c>
+      <c r="S14" t="n">
+        <v>6</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>51</v>
+      </c>
+      <c r="V14" t="n">
+        <v>3</v>
+      </c>
+      <c r="W14" t="n">
+        <v>31</v>
+      </c>
+      <c r="X14" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>123</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>121</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>119</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE14" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG14" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI14" t="n">
+        <v>8</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="n">
+        <v>3</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>6</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>1.385</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>1.417</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>P14</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3</v>
+      </c>
+      <c r="C15" t="n">
+        <v>27</v>
+      </c>
+      <c r="D15" t="n">
+        <v>3</v>
+      </c>
+      <c r="E15" t="n">
+        <v>24</v>
+      </c>
+      <c r="F15" t="n">
+        <v>3</v>
+      </c>
+      <c r="G15" t="n">
+        <v>37</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>6</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2</v>
+      </c>
+      <c r="K15" t="n">
+        <v>26</v>
+      </c>
+      <c r="L15" t="n">
+        <v>3</v>
+      </c>
+      <c r="M15" t="n">
+        <v>31</v>
+      </c>
+      <c r="N15" t="n">
+        <v>3</v>
+      </c>
+      <c r="O15" t="n">
+        <v>17</v>
+      </c>
+      <c r="P15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>30</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6</v>
+      </c>
+      <c r="S15" t="n">
+        <v>6</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>62</v>
+      </c>
+      <c r="V15" t="n">
+        <v>3</v>
+      </c>
+      <c r="W15" t="n">
+        <v>22</v>
+      </c>
+      <c r="X15" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>45</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>270</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>145</v>
+      </c>
+      <c r="AD15" t="n">
+        <v>4</v>
+      </c>
+      <c r="AE15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG15" t="n">
+        <v>30</v>
+      </c>
+      <c r="AH15" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI15" t="n">
+        <v>16</v>
+      </c>
+      <c r="AJ15" t="n">
+        <v>1</v>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO15" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD15" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE15" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF15" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG15" t="n">
+        <v>0.346</v>
+      </c>
+      <c r="BH15" t="n">
+        <v>0.417</v>
+      </c>
+      <c r="BI15" t="n">
+        <v>0.833</v>
+      </c>
+      <c r="BJ15" t="n">
+        <v>-0.125</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>P15</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="n">
+        <v>3</v>
+      </c>
+      <c r="E16" t="n">
+        <v>21</v>
+      </c>
+      <c r="F16" t="n">
+        <v>3</v>
+      </c>
+      <c r="G16" t="n">
+        <v>13</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>6</v>
+      </c>
+      <c r="J16" t="n">
+        <v>3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>22</v>
+      </c>
+      <c r="L16" t="n">
+        <v>3</v>
+      </c>
+      <c r="M16" t="n">
+        <v>18</v>
+      </c>
+      <c r="N16" t="n">
+        <v>3</v>
+      </c>
+      <c r="O16" t="n">
+        <v>10</v>
+      </c>
+      <c r="P16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>42</v>
+      </c>
+      <c r="R16" t="n">
+        <v>4</v>
+      </c>
+      <c r="S16" t="n">
+        <v>4</v>
+      </c>
+      <c r="T16" t="n">
+        <v>3</v>
+      </c>
+      <c r="U16" t="n">
+        <v>35</v>
+      </c>
+      <c r="V16" t="n">
+        <v>3</v>
+      </c>
+      <c r="W16" t="n">
+        <v>24</v>
+      </c>
+      <c r="X16" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y16" t="n">
+        <v>174</v>
+      </c>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="n">
+        <v>65</v>
+      </c>
+      <c r="AB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC16" t="n">
+        <v>70</v>
+      </c>
+      <c r="AD16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH16" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI16" t="n">
+        <v>35</v>
+      </c>
+      <c r="AJ16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="n">
+        <v>6</v>
+      </c>
+      <c r="AO16" t="n">
+        <v>4</v>
+      </c>
+      <c r="AP16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="n">
+        <v>3</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>-0.192</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>-0.625</v>
       </c>
     </row>
   </sheetData>

--- a/Data/permobil_data.xlsx
+++ b/Data/permobil_data.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BJ16"/>
+  <dimension ref="A1:BJ22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3288,6 +3288,720 @@
         <v>-0.625</v>
       </c>
     </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>P16</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>3</v>
+      </c>
+      <c r="C17" t="n">
+        <v>43</v>
+      </c>
+      <c r="D17" t="n">
+        <v>3</v>
+      </c>
+      <c r="E17" t="n">
+        <v>17</v>
+      </c>
+      <c r="F17" t="n">
+        <v>3</v>
+      </c>
+      <c r="G17" t="n">
+        <v>16</v>
+      </c>
+      <c r="H17" t="n">
+        <v>6</v>
+      </c>
+      <c r="I17" t="n">
+        <v>7</v>
+      </c>
+      <c r="J17" t="n">
+        <v>3</v>
+      </c>
+      <c r="K17" t="n">
+        <v>28</v>
+      </c>
+      <c r="L17" t="n">
+        <v>3</v>
+      </c>
+      <c r="M17" t="n">
+        <v>22</v>
+      </c>
+      <c r="N17" t="n">
+        <v>3</v>
+      </c>
+      <c r="O17" t="n">
+        <v>16</v>
+      </c>
+      <c r="P17" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>50</v>
+      </c>
+      <c r="R17" t="n">
+        <v>5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>7</v>
+      </c>
+      <c r="T17" t="n">
+        <v>3</v>
+      </c>
+      <c r="U17" t="n">
+        <v>35</v>
+      </c>
+      <c r="V17" t="n">
+        <v>3</v>
+      </c>
+      <c r="W17" t="n">
+        <v>14</v>
+      </c>
+      <c r="X17" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>106</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>154</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>77</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AE17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG17" t="n">
+        <v>10</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>6</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>-0.231</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>-0.417</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>-0.167</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>P17</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3</v>
+      </c>
+      <c r="C18" t="n">
+        <v>34</v>
+      </c>
+      <c r="D18" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" t="n">
+        <v>35</v>
+      </c>
+      <c r="F18" t="n">
+        <v>3</v>
+      </c>
+      <c r="G18" t="n">
+        <v>25</v>
+      </c>
+      <c r="H18" t="n">
+        <v>6</v>
+      </c>
+      <c r="I18" t="n">
+        <v>6</v>
+      </c>
+      <c r="J18" t="n">
+        <v>3</v>
+      </c>
+      <c r="K18" t="n">
+        <v>41</v>
+      </c>
+      <c r="L18" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" t="n">
+        <v>32</v>
+      </c>
+      <c r="N18" t="n">
+        <v>3</v>
+      </c>
+      <c r="O18" t="n">
+        <v>12</v>
+      </c>
+      <c r="P18" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>67</v>
+      </c>
+      <c r="R18" t="n">
+        <v>5</v>
+      </c>
+      <c r="S18" t="n">
+        <v>5</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>74</v>
+      </c>
+      <c r="V18" t="n">
+        <v>3</v>
+      </c>
+      <c r="W18" t="n">
+        <v>20</v>
+      </c>
+      <c r="X18" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>154</v>
+      </c>
+      <c r="Z18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>63</v>
+      </c>
+      <c r="AD18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>37</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" t="inlineStr"/>
+      <c r="AN18" t="n">
+        <v>5</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>6</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" t="inlineStr"/>
+      <c r="AR18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" t="inlineStr"/>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AU18" t="inlineStr"/>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="inlineStr"/>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr"/>
+      <c r="BA18" t="inlineStr"/>
+      <c r="BB18" t="n">
+        <v>6</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>0.6919999999999999</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>1</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>P18</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>3</v>
+      </c>
+      <c r="C19" t="n">
+        <v>10</v>
+      </c>
+      <c r="D19" t="n">
+        <v>3</v>
+      </c>
+      <c r="E19" t="n">
+        <v>17</v>
+      </c>
+      <c r="F19" t="n">
+        <v>3</v>
+      </c>
+      <c r="G19" t="n">
+        <v>14</v>
+      </c>
+      <c r="H19" t="n">
+        <v>7</v>
+      </c>
+      <c r="I19" t="n">
+        <v>7</v>
+      </c>
+      <c r="J19" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>23</v>
+      </c>
+      <c r="L19" t="n">
+        <v>3</v>
+      </c>
+      <c r="M19" t="n">
+        <v>14</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3</v>
+      </c>
+      <c r="O19" t="n">
+        <v>5</v>
+      </c>
+      <c r="P19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>14</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7</v>
+      </c>
+      <c r="S19" t="n">
+        <v>7</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>15</v>
+      </c>
+      <c r="V19" t="n">
+        <v>3</v>
+      </c>
+      <c r="W19" t="n">
+        <v>27</v>
+      </c>
+      <c r="X19" t="n">
+        <v>3</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>31</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>78</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>9</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>3</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" t="inlineStr"/>
+      <c r="AN19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ19" t="inlineStr"/>
+      <c r="AR19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS19" t="inlineStr"/>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AU19" t="inlineStr"/>
+      <c r="AV19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW19" t="inlineStr"/>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr"/>
+      <c r="BA19" t="inlineStr"/>
+      <c r="BB19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>5</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>7</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.115</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>1.25</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>P19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr"/>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr"/>
+      <c r="S20" t="inlineStr"/>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr"/>
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr"/>
+      <c r="X20" t="inlineStr"/>
+      <c r="Y20" t="inlineStr"/>
+      <c r="Z20" t="inlineStr"/>
+      <c r="AA20" t="inlineStr"/>
+      <c r="AB20" t="inlineStr"/>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr"/>
+      <c r="AE20" t="inlineStr"/>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="inlineStr"/>
+      <c r="AH20" t="inlineStr"/>
+      <c r="AI20" t="inlineStr"/>
+      <c r="AJ20" t="inlineStr"/>
+      <c r="AK20" t="inlineStr"/>
+      <c r="AL20" t="inlineStr"/>
+      <c r="AM20" t="inlineStr"/>
+      <c r="AN20" t="inlineStr"/>
+      <c r="AO20" t="inlineStr"/>
+      <c r="AP20" t="inlineStr"/>
+      <c r="AQ20" t="inlineStr"/>
+      <c r="AR20" t="inlineStr"/>
+      <c r="AS20" t="inlineStr"/>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AU20" t="inlineStr"/>
+      <c r="AV20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr"/>
+      <c r="AX20" t="inlineStr"/>
+      <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr"/>
+      <c r="BA20" t="inlineStr"/>
+      <c r="BB20" t="inlineStr"/>
+      <c r="BC20" t="inlineStr"/>
+      <c r="BD20" t="inlineStr"/>
+      <c r="BE20" t="inlineStr"/>
+      <c r="BF20" t="inlineStr"/>
+      <c r="BG20" t="inlineStr"/>
+      <c r="BH20" t="inlineStr"/>
+      <c r="BI20" t="inlineStr"/>
+      <c r="BJ20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>P20</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr"/>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr"/>
+      <c r="S21" t="inlineStr"/>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr"/>
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr"/>
+      <c r="X21" t="inlineStr"/>
+      <c r="Y21" t="inlineStr"/>
+      <c r="Z21" t="inlineStr"/>
+      <c r="AA21" t="inlineStr"/>
+      <c r="AB21" t="inlineStr"/>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr"/>
+      <c r="AE21" t="inlineStr"/>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="inlineStr"/>
+      <c r="AH21" t="inlineStr"/>
+      <c r="AI21" t="inlineStr"/>
+      <c r="AJ21" t="inlineStr"/>
+      <c r="AK21" t="inlineStr"/>
+      <c r="AL21" t="inlineStr"/>
+      <c r="AM21" t="inlineStr"/>
+      <c r="AN21" t="inlineStr"/>
+      <c r="AO21" t="inlineStr"/>
+      <c r="AP21" t="inlineStr"/>
+      <c r="AQ21" t="inlineStr"/>
+      <c r="AR21" t="inlineStr"/>
+      <c r="AS21" t="inlineStr"/>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AU21" t="inlineStr"/>
+      <c r="AV21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr"/>
+      <c r="AX21" t="inlineStr"/>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr"/>
+      <c r="BA21" t="inlineStr"/>
+      <c r="BB21" t="inlineStr"/>
+      <c r="BC21" t="inlineStr"/>
+      <c r="BD21" t="inlineStr"/>
+      <c r="BE21" t="inlineStr"/>
+      <c r="BF21" t="inlineStr"/>
+      <c r="BG21" t="inlineStr"/>
+      <c r="BH21" t="inlineStr"/>
+      <c r="BI21" t="inlineStr"/>
+      <c r="BJ21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>P22</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr"/>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr"/>
+      <c r="S22" t="inlineStr"/>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr"/>
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr"/>
+      <c r="X22" t="inlineStr"/>
+      <c r="Y22" t="inlineStr"/>
+      <c r="Z22" t="inlineStr"/>
+      <c r="AA22" t="inlineStr"/>
+      <c r="AB22" t="inlineStr"/>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr"/>
+      <c r="AE22" t="inlineStr"/>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="inlineStr"/>
+      <c r="AH22" t="inlineStr"/>
+      <c r="AI22" t="inlineStr"/>
+      <c r="AJ22" t="inlineStr"/>
+      <c r="AK22" t="inlineStr"/>
+      <c r="AL22" t="inlineStr"/>
+      <c r="AM22" t="inlineStr"/>
+      <c r="AN22" t="inlineStr"/>
+      <c r="AO22" t="inlineStr"/>
+      <c r="AP22" t="inlineStr"/>
+      <c r="AQ22" t="inlineStr"/>
+      <c r="AR22" t="inlineStr"/>
+      <c r="AS22" t="inlineStr"/>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AU22" t="inlineStr"/>
+      <c r="AV22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr"/>
+      <c r="AX22" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr"/>
+      <c r="BA22" t="inlineStr"/>
+      <c r="BB22" t="inlineStr"/>
+      <c r="BC22" t="inlineStr"/>
+      <c r="BD22" t="inlineStr"/>
+      <c r="BE22" t="inlineStr"/>
+      <c r="BF22" t="inlineStr"/>
+      <c r="BG22" t="inlineStr"/>
+      <c r="BH22" t="inlineStr"/>
+      <c r="BI22" t="inlineStr"/>
+      <c r="BJ22" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
